--- a/04_DESIGN_TABLES/DesignTable_2702_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2702_SW2.xlsx
@@ -837,13 +837,13 @@
         <v>0.375</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1025,13 +1025,13 @@
         <v>0.22</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         <v>0.22</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         <v>0.28125</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         <v>0.28125</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         <v>0.375</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1975,13 +1975,13 @@
         <v>0.44</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
         <v>0.53125</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -2356,13 +2356,13 @@
         <v>0.65625</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -2549,13 +2549,13 @@
         <v>0.65625</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         <v>0.8125</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.4691</v>
+        <v>0.4686</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4691</v>
+        <v>0.4686</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.93819</v>
+        <v>0.93769</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
